--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4114A3D6-F32A-464D-A745-59BDF589C448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D159606-9D1C-4D4D-B936-E5E8911DC34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Seida</t>
   </si>
   <si>
-    <t>01/01/1983</t>
+    <t>01/01/1983 00:00:00</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -67,10 +67,10 @@
     <t>F</t>
   </si>
   <si>
-    <t>10/09/2024</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
+    <t>10/09/2024 00:00:00</t>
+  </si>
+  <si>
+    <t>01/01/1900 00:00:00</t>
   </si>
   <si>
     <t>ADDOUT SOULEMAN</t>
@@ -88,10 +88,10 @@
     <t>Monira</t>
   </si>
   <si>
-    <t>01/01/1987</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
+    <t>01/01/1987 00:00:00</t>
+  </si>
+  <si>
+    <t>25/09/2025 00:00:00</t>
   </si>
   <si>
     <t>AJAYI</t>
@@ -109,10 +109,10 @@
     <t>Mudather</t>
   </si>
   <si>
-    <t>08/04/1999</t>
-  </si>
-  <si>
-    <t>25/11/2024</t>
+    <t>08/04/1999 00:00:00</t>
+  </si>
+  <si>
+    <t>25/11/2024 00:00:00</t>
   </si>
   <si>
     <t>ANTURIA</t>
@@ -130,13 +130,13 @@
     <t>Elizandra Maria</t>
   </si>
   <si>
-    <t>12/02/2006</t>
+    <t>12/02/2006 00:00:00</t>
   </si>
   <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>09/10/2025</t>
+    <t>09/10/2025 00:00:00</t>
   </si>
   <si>
     <t>EBRAHIM DUD</t>
@@ -145,7 +145,7 @@
     <t>Nabil</t>
   </si>
   <si>
-    <t>16/09/2025</t>
+    <t>16/09/2025 00:00:00</t>
   </si>
   <si>
     <t>EGBOYE</t>
@@ -169,13 +169,13 @@
     <t>Gyurme</t>
   </si>
   <si>
-    <t>08/02/1997</t>
+    <t>08/02/1997 00:00:00</t>
   </si>
   <si>
     <t>Tibet</t>
   </si>
   <si>
-    <t>08/10/2025</t>
+    <t>08/10/2025 00:00:00</t>
   </si>
   <si>
     <t>KHAROT</t>
@@ -193,13 +193,13 @@
     <t>Ilham</t>
   </si>
   <si>
-    <t>15/08/2002</t>
+    <t>15/08/2002 00:00:00</t>
   </si>
   <si>
     <t>Algérie</t>
   </si>
   <si>
-    <t>07/11/2025</t>
+    <t>07/11/2025 00:00:00</t>
   </si>
   <si>
     <t>MOUSSA BABAY</t>
@@ -235,10 +235,10 @@
     <t>Mohammed</t>
   </si>
   <si>
-    <t>01/01/1994</t>
-  </si>
-  <si>
-    <t>17/09/2024</t>
+    <t>01/01/1994 00:00:00</t>
+  </si>
+  <si>
+    <t>17/09/2024 00:00:00</t>
   </si>
   <si>
     <t>SALAH</t>
@@ -250,7 +250,7 @@
     <t>Ahmed</t>
   </si>
   <si>
-    <t>01/01/1998</t>
+    <t>01/01/1998 00:00:00</t>
   </si>
   <si>
     <t>Somalie</t>
@@ -262,10 +262,10 @@
     <t>Nyima</t>
   </si>
   <si>
-    <t>10/06/1997</t>
-  </si>
-  <si>
-    <t>07/10/2025</t>
+    <t>10/06/1997 00:00:00</t>
+  </si>
+  <si>
+    <t>07/10/2025 00:00:00</t>
   </si>
   <si>
     <t>TOLA</t>
@@ -274,7 +274,7 @@
     <t>Boja</t>
   </si>
   <si>
-    <t>27/08/2004</t>
+    <t>27/08/2004 00:00:00</t>
   </si>
   <si>
     <t>Éthiopie</t>
@@ -295,7 +295,7 @@
     <t>Karma</t>
   </si>
   <si>
-    <t>15/05/1988</t>
+    <t>15/05/1988 00:00:00</t>
   </si>
   <si>
     <t>Chine</t>
@@ -785,7 +785,7 @@
     <col min="5" max="5" width="11.85546875" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D159606-9D1C-4D4D-B936-E5E8911DC34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99B26D4-10D1-4C04-98C3-3E49E11E45A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
     <t>Seida</t>
   </si>
   <si>
-    <t>01/01/1983 00:00:00</t>
+    <t>01/01/1983</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -67,10 +67,10 @@
     <t>F</t>
   </si>
   <si>
-    <t>10/09/2024 00:00:00</t>
-  </si>
-  <si>
-    <t>01/01/1900 00:00:00</t>
+    <t>10/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
   </si>
   <si>
     <t>ADDOUT SOULEMAN</t>
@@ -88,10 +88,10 @@
     <t>Monira</t>
   </si>
   <si>
-    <t>01/01/1987 00:00:00</t>
-  </si>
-  <si>
-    <t>25/09/2025 00:00:00</t>
+    <t>01/01/1987</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
   </si>
   <si>
     <t>AJAYI</t>
@@ -109,10 +109,10 @@
     <t>Mudather</t>
   </si>
   <si>
-    <t>08/04/1999 00:00:00</t>
-  </si>
-  <si>
-    <t>25/11/2024 00:00:00</t>
+    <t>08/04/1999</t>
+  </si>
+  <si>
+    <t>25/11/2024</t>
   </si>
   <si>
     <t>ANTURIA</t>
@@ -130,13 +130,13 @@
     <t>Elizandra Maria</t>
   </si>
   <si>
-    <t>12/02/2006 00:00:00</t>
+    <t>12/02/2006</t>
   </si>
   <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>09/10/2025 00:00:00</t>
+    <t>09/10/2025</t>
   </si>
   <si>
     <t>EBRAHIM DUD</t>
@@ -145,7 +145,7 @@
     <t>Nabil</t>
   </si>
   <si>
-    <t>16/09/2025 00:00:00</t>
+    <t>16/09/2025</t>
   </si>
   <si>
     <t>EGBOYE</t>
@@ -169,13 +169,13 @@
     <t>Gyurme</t>
   </si>
   <si>
-    <t>08/02/1997 00:00:00</t>
+    <t>08/02/1997</t>
   </si>
   <si>
     <t>Tibet</t>
   </si>
   <si>
-    <t>08/10/2025 00:00:00</t>
+    <t>08/10/2025</t>
   </si>
   <si>
     <t>KHAROT</t>
@@ -193,13 +193,13 @@
     <t>Ilham</t>
   </si>
   <si>
-    <t>15/08/2002 00:00:00</t>
+    <t>15/08/2002</t>
   </si>
   <si>
     <t>Algérie</t>
   </si>
   <si>
-    <t>07/11/2025 00:00:00</t>
+    <t>07/11/2025</t>
   </si>
   <si>
     <t>MOUSSA BABAY</t>
@@ -235,10 +235,10 @@
     <t>Mohammed</t>
   </si>
   <si>
-    <t>01/01/1994 00:00:00</t>
-  </si>
-  <si>
-    <t>17/09/2024 00:00:00</t>
+    <t>01/01/1994</t>
+  </si>
+  <si>
+    <t>17/09/2024</t>
   </si>
   <si>
     <t>SALAH</t>
@@ -250,7 +250,7 @@
     <t>Ahmed</t>
   </si>
   <si>
-    <t>01/01/1998 00:00:00</t>
+    <t>01/01/1998</t>
   </si>
   <si>
     <t>Somalie</t>
@@ -262,10 +262,10 @@
     <t>Nyima</t>
   </si>
   <si>
-    <t>10/06/1997 00:00:00</t>
-  </si>
-  <si>
-    <t>07/10/2025 00:00:00</t>
+    <t>10/06/1997</t>
+  </si>
+  <si>
+    <t>07/10/2025</t>
   </si>
   <si>
     <t>TOLA</t>
@@ -274,7 +274,7 @@
     <t>Boja</t>
   </si>
   <si>
-    <t>27/08/2004 00:00:00</t>
+    <t>27/08/2004</t>
   </si>
   <si>
     <t>Éthiopie</t>
@@ -295,7 +295,7 @@
     <t>Karma</t>
   </si>
   <si>
-    <t>15/05/1988 00:00:00</t>
+    <t>15/05/1988</t>
   </si>
   <si>
     <t>Chine</t>
@@ -785,7 +785,7 @@
     <col min="5" max="5" width="11.85546875" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="9" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99B26D4-10D1-4C04-98C3-3E49E11E45A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02D0774-5343-48E7-903D-F928C05C6867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B02D0774-5343-48E7-903D-F928C05C6867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF9F766-9E8C-4F43-92D8-E769898F4EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="96">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -239,6 +239,18 @@
   </si>
   <si>
     <t>17/09/2024</t>
+  </si>
+  <si>
+    <t>QQQQ</t>
+  </si>
+  <si>
+    <t>Qqqq</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>29/09/2026</t>
   </si>
   <si>
     <t>SALAH</t>
@@ -1338,19 +1350,19 @@
         <v>72</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -1361,22 +1373,22 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>18</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -1396,13 +1408,13 @@
         <v>79</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -1422,13 +1434,13 @@
         <v>83</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>18</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -1445,16 +1457,16 @@
         <v>86</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>15</v>
+        <v>87</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F27" s="10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -1465,38 +1477,52 @@
         <v>25</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F28" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="A29" s="4">
+        <v>26</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G29" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A29" s="11">
-        <v>26</v>
-      </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="14"/>
+      <c r="H29" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="30" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A30" s="11">

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF9F766-9E8C-4F43-92D8-E769898F4EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B027C0F-BEAD-4CC1-96E0-9EE50955EF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B027C0F-BEAD-4CC1-96E0-9EE50955EF2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1357E2-40D2-4590-9C06-285CA5059D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -239,18 +239,6 @@
   </si>
   <si>
     <t>17/09/2024</t>
-  </si>
-  <si>
-    <t>QQQQ</t>
-  </si>
-  <si>
-    <t>Qqqq</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>29/09/2026</t>
   </si>
   <si>
     <t>SALAH</t>
@@ -1350,19 +1338,19 @@
         <v>72</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="D23" s="10" t="s">
         <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -1373,22 +1361,22 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>18</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -1408,13 +1396,13 @@
         <v>79</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>18</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -1434,13 +1422,13 @@
         <v>83</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>18</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -1457,16 +1445,16 @@
         <v>86</v>
       </c>
       <c r="D27" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="F27" s="10" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -1477,52 +1465,38 @@
         <v>25</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="D28" s="10" t="s">
         <v>90</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>15</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>91</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A29" s="4">
+      <c r="A29" s="11">
         <v>26</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="14"/>
     </row>
     <row r="30" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A30" s="11">
